--- a/MIS3371 Contribution Tracker.xlsx
+++ b/MIS3371 Contribution Tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/cnguy231_cougarnet_uh_edu/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A17A4CE-04BC-4567-A110-33AB4F329825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04A82DC7-1E8B-4AC3-B4E2-57BF05D01002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="23020" windowHeight="14620" xr2:uid="{30688633-D282-4B4F-9CFE-0F6485F2C445}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Team Member</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Sept 16 - Live Build</t>
+  </si>
+  <si>
+    <t>09/21 - Live Build: CSS</t>
   </si>
   <si>
     <t>Lana Tran</t>
@@ -142,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -180,11 +183,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -215,6 +229,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,13 +567,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7064EB42-CD23-49CB-9B54-70C1C4D8618F}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="8" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="78.95" thickBot="1">
+    <row r="1" spans="1:9" ht="78.95" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -578,11 +595,14 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5"/>
+      <c r="H1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11"/>
     </row>
-    <row r="2" spans="1:8" ht="26.45" thickBot="1">
+    <row r="2" spans="1:9" ht="26.45" thickBot="1">
       <c r="A2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="7">
         <v>100</v>
@@ -602,11 +622,13 @@
       <c r="G2" s="8">
         <v>100</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="26.45" thickBot="1">
+    <row r="3" spans="1:9" ht="26.45" thickBot="1">
       <c r="A3" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="7">
         <v>100</v>
@@ -626,11 +648,13 @@
       <c r="G3" s="8">
         <v>100</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="26.45" thickBot="1">
+    <row r="4" spans="1:9" ht="26.45" thickBot="1">
       <c r="A4" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="7">
         <v>100</v>
@@ -650,11 +674,13 @@
       <c r="G4" s="8">
         <v>100</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="26.45" thickBot="1">
+    <row r="5" spans="1:9" ht="26.45" thickBot="1">
       <c r="A5" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7">
         <v>100</v>
@@ -674,11 +700,13 @@
       <c r="G5" s="8">
         <v>100</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="26.45" thickBot="1">
+    <row r="6" spans="1:9" ht="26.45" thickBot="1">
       <c r="A6" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="7">
         <v>100</v>
@@ -698,9 +726,11 @@
       <c r="G6" s="8">
         <v>100</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="5">
+        <v>100</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" ht="15" thickBot="1">
+    <row r="7" spans="1:9" ht="15" thickBot="1">
       <c r="A7" s="5"/>
       <c r="B7" s="10"/>
       <c r="C7" s="5"/>
@@ -709,6 +739,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -716,20 +747,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="41165478-3f5a-49d8-b2c1-4a6763303165" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -883,11 +914,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38074111-C309-4A5A-B2E4-375C5B6267CD}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793C2600-2A3D-47D3-BF82-7EC71AE0048B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
